--- a/文档/策划/技能配置.xlsx
+++ b/文档/策划/技能配置.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="103">
   <si>
     <t>id</t>
   </si>
@@ -119,6 +119,237 @@
   </si>
   <si>
     <t>配置技能触发时的效果，有很多效果，但是不知道怎么配</t>
+  </si>
+  <si>
+    <t>Ability ld</t>
+  </si>
+  <si>
+    <t>Total Time</t>
+  </si>
+  <si>
+    <t>技能持续时间</t>
+  </si>
+  <si>
+    <t>0bj Asset</t>
+  </si>
+  <si>
+    <t>技能执行体的关联对象</t>
+  </si>
+  <si>
+    <t>技能表现是特效还是模型，枚举怎么配不知道</t>
+  </si>
+  <si>
+    <t>Target Input Type</t>
+  </si>
+  <si>
+    <t>目标传入类型</t>
+  </si>
+  <si>
+    <t>传入目标实体还是传入目标点，啥意思</t>
+  </si>
+  <si>
+    <t>Range Indicator Obj Asset</t>
+  </si>
+  <si>
+    <t>范围指示器对象资产</t>
+  </si>
+  <si>
+    <t>不懂</t>
+  </si>
+  <si>
+    <t>Point Indicator Obj Asset</t>
+  </si>
+  <si>
+    <t>点指标对象资产</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direction Indicator ObjAsse </t>
+  </si>
+  <si>
+    <t>方向指示器资产</t>
+  </si>
+  <si>
+    <t>偏移</t>
+  </si>
+  <si>
+    <t>Execute Clips</t>
+  </si>
+  <si>
+    <t>Start Time</t>
+  </si>
+  <si>
+    <t>起始时间</t>
+  </si>
+  <si>
+    <t>End Time</t>
+  </si>
+  <si>
+    <t>结束时间</t>
+  </si>
+  <si>
+    <t>Execute Clip Type</t>
+  </si>
+  <si>
+    <t>定义改阶段内有那些表现</t>
+  </si>
+  <si>
+    <t>ItemExecute = 0,       // 执行物体（如碰撞体、飞行物等）
+ActionEvent = 1,       // 触发事件
+Animation = 2,         // 播放动画
+Audio = 3,             // 播放音效
+ParticleEffect = 4    // 播放粒子特效</t>
+  </si>
+  <si>
+    <t>Action Event Data</t>
+  </si>
+  <si>
+    <t>事件控制</t>
+  </si>
+  <si>
+    <t>用于描述事件触发的相关数据（如触发类型、触发效果等）</t>
+  </si>
+  <si>
+    <t>Fire Type</t>
+  </si>
+  <si>
+    <t>触发行为点类型</t>
+  </si>
+  <si>
+    <t>不触发= 0,
+初始触发= 1 
+碰撞触发单次= 2,
+结束触发=3,
+碰撞触发多次，就是每次碰撞都触发= 4,</t>
+  </si>
+  <si>
+    <t>Action Event Type</t>
+  </si>
+  <si>
+    <t>触发事件类型</t>
+  </si>
+  <si>
+    <t>0= 触发一个效果赋给目标（如伤害、治疗、状态等）。
+1=触发一个新的技能执行体（如召唤物、连锁技能等）</t>
+  </si>
+  <si>
+    <t>Execute Trigger</t>
+  </si>
+  <si>
+    <t>触发效果类型</t>
+  </si>
+  <si>
+    <t>Action Event Type=0 的时候配置具体效果枚举</t>
+  </si>
+  <si>
+    <t>Effect Apply Target</t>
+  </si>
+  <si>
+    <t>效果应用目标</t>
+  </si>
+  <si>
+    <t>0=敌方，1=己方</t>
+  </si>
+  <si>
+    <t>New Execution</t>
+  </si>
+  <si>
+    <t>定义新执行体的名称或标识</t>
+  </si>
+  <si>
+    <t>ltem Data</t>
+  </si>
+  <si>
+    <t>Execute Type</t>
+  </si>
+  <si>
+    <t>技能物体的执行类型</t>
+  </si>
+  <si>
+    <t>• OutOfHand：脱手执行（如飞行物）。
+• InHand：执手执行（如近战攻击</t>
+  </si>
+  <si>
+    <t>Move Type</t>
+  </si>
+  <si>
+    <t>• FixedPosition：固定位置。
+• TargetFly：目标飞行。
+• PathFly：路径飞行</t>
+  </si>
+  <si>
+    <t>Fixed Point</t>
+  </si>
+  <si>
+    <t>具体位置</t>
+  </si>
+  <si>
+    <t>如果Move Type为固定位置，配置具体位置</t>
+  </si>
+  <si>
+    <t>物体资源</t>
+  </si>
+  <si>
+    <t>关联物体的资源，具体模型或特效</t>
+  </si>
+  <si>
+    <t>速度</t>
+  </si>
+  <si>
+    <t>物体运动速度</t>
+  </si>
+  <si>
+    <t>Bezier Curve</t>
+  </si>
+  <si>
+    <t>运动路径</t>
+  </si>
+  <si>
+    <t>Move Type为路径飞行，定义路径函数</t>
+  </si>
+  <si>
+    <t>Path Execute Point</t>
+  </si>
+  <si>
+    <t>路径执行点</t>
+  </si>
+  <si>
+    <t>Animation Data</t>
+  </si>
+  <si>
+    <t>动作</t>
+  </si>
+  <si>
+    <t>Animation Clip</t>
+  </si>
+  <si>
+    <t>配置攻击动作文件</t>
+  </si>
+  <si>
+    <t>Audio Data</t>
+  </si>
+  <si>
+    <t>音频</t>
+  </si>
+  <si>
+    <t>音频剪辑</t>
+  </si>
+  <si>
+    <t>配置音频文件</t>
+  </si>
+  <si>
+    <t>Particle Effect Data</t>
+  </si>
+  <si>
+    <t>特效</t>
+  </si>
+  <si>
+    <t>粒子效果</t>
+  </si>
+  <si>
+    <t>配置特效文件</t>
+  </si>
+  <si>
+    <t>Effect Type Name</t>
   </si>
 </sst>
 </file>
@@ -734,12 +965,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -832,8 +1069,92 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10420350" y="333375"/>
+          <a:off x="11049000" y="333375"/>
           <a:ext cx="4229100" cy="4905375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11049000" y="5829300"/>
+          <a:ext cx="4248150" cy="3638550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11049000" y="9772650"/>
+          <a:ext cx="4124325" cy="5734050"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1099,10 +1420,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:C14"/>
+  <dimension ref="A3:C82"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="24.625" customWidth="1"/>
+    <col min="1" max="1" width="32.875" customWidth="1"/>
     <col min="2" max="2" width="33.875" customWidth="1"/>
     <col min="3" max="3" width="60.25" style="1" customWidth="1"/>
   </cols>
@@ -1217,6 +1538,308 @@
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>48</v>
+      </c>
+      <c r="B55" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>50</v>
+      </c>
+      <c r="B56" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" ht="67.5" spans="1:3">
+      <c r="A57" t="s">
+        <v>52</v>
+      </c>
+      <c r="B57" t="s">
+        <v>53</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>55</v>
+      </c>
+      <c r="B58" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" ht="67.5" spans="1:3">
+      <c r="A59" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>59</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" ht="27" spans="1:3">
+      <c r="A60" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B60" t="s">
+        <v>62</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B61" t="s">
+        <v>65</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="65" ht="27" spans="1:3">
+      <c r="A65" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B65" t="s">
+        <v>74</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="66" ht="40.5" spans="1:3">
+      <c r="A66" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B67" t="s">
+        <v>79</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B68" t="s">
+        <v>81</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B69" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B70" t="s">
+        <v>86</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>90</v>
+      </c>
+      <c r="B74" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>94</v>
+      </c>
+      <c r="B77" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>98</v>
+      </c>
+      <c r="B80" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="2" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/文档/策划/技能配置.xlsx
+++ b/文档/策划/技能配置.xlsx
@@ -100,7 +100,11 @@
     <t>添加技能效果目标</t>
   </si>
   <si>
-    <t>技能的作用对象，包括技能目标，附身目标，自己等</t>
+    <t>技能的作用对象，包括技能目标，附身目标，自己等；
+技能目标 = 0,
+附身对象 = 1,
+自身 = 2,
+其他 = 3,</t>
   </si>
   <si>
     <t>State Check List</t>
@@ -109,7 +113,7 @@
     <t>状态检查清单</t>
   </si>
   <si>
-    <t>触发条件达成的时候额外满足什么状态，可配置多个状态同时满足，但是具体怎么配状态，未知</t>
+    <t>触发条件达成的时候额外满足什么状态，可配置多个状态的list同时满足，但是具体怎么配状态，未知</t>
   </si>
   <si>
     <t>Trigger Effects</t>
@@ -118,7 +122,7 @@
     <t>触发效果</t>
   </si>
   <si>
-    <t>配置技能触发时的效果，有很多效果，但是不知道怎么配</t>
+    <t>配置技能触发时的效果，有很多效果，但是不知道怎么配,</t>
   </si>
   <si>
     <t>Ability ld</t>
@@ -965,15 +969,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1051,7 +1052,7 @@
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1111,7 +1112,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11049000" y="5829300"/>
+          <a:off x="11049000" y="6515100"/>
           <a:ext cx="4248150" cy="3638550"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1153,7 +1154,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11049000" y="9772650"/>
+          <a:off x="11049000" y="10458450"/>
           <a:ext cx="4124325" cy="5734050"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1507,7 +1508,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" ht="67.5" spans="1:3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1777,7 +1778,7 @@
       </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="3" t="s">
+      <c r="A72" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C72" s="1" t="s">
@@ -1785,7 +1786,7 @@
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="3" t="s">
+      <c r="A73" s="2" t="s">
         <v>46</v>
       </c>
     </row>

--- a/文档/策划/技能配置.xlsx
+++ b/文档/策划/技能配置.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="24045" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -965,15 +965,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1163,6 +1160,129 @@
         <a:ln w="9525">
           <a:noFill/>
         </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15487650" y="381000"/>
+          <a:ext cx="4953000" cy="5391150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>153670</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>512445</xdr:colOff>
+      <xdr:row>206</xdr:row>
+      <xdr:rowOff>113665</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1" descr="AbilityConfigObject"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1525270" y="9525"/>
+          <a:ext cx="9274175" cy="35422840"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>264160</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>100965</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>43815</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2" descr="Execution Object"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14665960" y="2329815"/>
+          <a:ext cx="8413115" cy="10058400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1777,7 +1897,7 @@
       </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="3" t="s">
+      <c r="A72" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C72" s="1" t="s">
@@ -1785,7 +1905,7 @@
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="3" t="s">
+      <c r="A73" s="2" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1859,6 +1979,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
